--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.8021637796297</v>
+        <v>3.867851614189827</v>
       </c>
       <c r="D2" t="n">
-        <v>23.9945644350409</v>
+        <v>3.899116720694146</v>
       </c>
       <c r="E2" t="n">
-        <v>9.035887778934464</v>
+        <v>1.46833176407685</v>
       </c>
       <c r="F2" t="n">
-        <v>8.92623069652678</v>
+        <v>1.450512488185602</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.707166419933982</v>
+        <v>0.6024145432392721</v>
       </c>
       <c r="D3" t="n">
-        <v>3.859464052906117</v>
+        <v>0.6271629085972441</v>
       </c>
       <c r="E3" t="n">
-        <v>9.035887778934464</v>
+        <v>1.46833176407685</v>
       </c>
       <c r="F3" t="n">
-        <v>8.92623069652678</v>
+        <v>1.450512488185602</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.85797098739668</v>
+        <v>3.551920285451961</v>
       </c>
       <c r="D4" t="n">
-        <v>21.74059406816591</v>
+        <v>3.53284653607696</v>
       </c>
       <c r="E4" t="n">
-        <v>9.035887778934464</v>
+        <v>1.46833176407685</v>
       </c>
       <c r="F4" t="n">
-        <v>8.92623069652678</v>
+        <v>1.450512488185602</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.01669039065451</v>
+        <v>4.877712188481358</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82902763138224</v>
+        <v>4.847216990099613</v>
       </c>
       <c r="E5" t="n">
-        <v>9.035887778934464</v>
+        <v>1.46833176407685</v>
       </c>
       <c r="F5" t="n">
-        <v>8.92623069652678</v>
+        <v>1.450512488185602</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.39489286485788</v>
+        <v>4.126670090539406</v>
       </c>
       <c r="D6" t="n">
-        <v>25.14246617860603</v>
+        <v>4.08565075402348</v>
       </c>
       <c r="E6" t="n">
-        <v>9.035887778934464</v>
+        <v>1.46833176407685</v>
       </c>
       <c r="F6" t="n">
-        <v>8.92623069652678</v>
+        <v>1.450512488185602</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
